--- a/results/ntnu_datasets.xlsx
+++ b/results/ntnu_datasets.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.84]</t>
+          <t>0.82 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.84]</t>
+          <t>0.82 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.84]</t>
+          <t>0.82 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.84]</t>
+          <t>0.82 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.84]</t>
+          <t>0.82 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.84]</t>
+          <t>0.82 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.84]</t>
+          <t>0.82 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.84]</t>
+          <t>0.82 [0.80, 0.85]</t>
         </is>
       </c>
     </row>
@@ -515,116 +515,116 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.79 [0.74, 0.83]</t>
+          <t>0.79 [0.73, 0.84]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.83 [0.78, 0.88]</t>
+          <t>0.83 [0.77, 0.89]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.84]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.33 [0.31, 0.35]</t>
+          <t>0.33 [0.30, 0.35]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.88 [0.86, 0.89]</t>
+          <t>0.88 [0.86, 0.90]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.45 [0.37, 0.53]</t>
+          <t>0.45 [0.35, 0.55]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.82 [0.78, 0.85]</t>
+          <t>0.82 [0.78, 0.86]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.88 [0.81, 0.96]</t>
+          <t>0.88 [0.79, 0.98]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.71 [0.64, 0.77]</t>
+          <t>0.77 [0.74, 0.80]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.93 [0.91, 0.95]</t>
+          <t>0.77 [0.74, 0.80]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.90 [0.89, 0.92]</t>
+          <t>0.77 [0.74, 0.80]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.30 [0.28, 0.33]</t>
+          <t>0.77 [0.74, 0.80]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.88 [0.86, 0.90]</t>
+          <t>0.77 [0.74, 0.80]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.49 [0.41, 0.58]</t>
+          <t>0.77 [0.74, 0.80]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.76 [0.72, 0.81]</t>
+          <t>0.77 [0.74, 0.80]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.90 [0.85, 0.94]</t>
+          <t>0.77 [0.74, 0.80]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.96 [0.92, 1.00]</t>
+          <t>0.71 [0.63, 0.79]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79 [0.73, 0.86]</t>
+          <t>0.93 [0.91, 0.96]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.75 [0.71, 0.79]</t>
+          <t>0.90 [0.88, 0.92]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.40 [0.36, 0.43]</t>
+          <t>0.30 [0.28, 0.33]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -634,137 +634,153 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.48 [0.39, 0.57]</t>
+          <t>0.49 [0.39, 0.59]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.90 [0.88, 0.92]</t>
+          <t>0.76 [0.71, 0.82]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.93 [0.85, 1.00]</t>
+          <t>0.90 [0.84, 0.95]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>208.41 ± 83.13</t>
+          <t>0.96 [0.91, 1.00]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>558.09 ± 298.19</t>
+          <t>0.79 [0.72, 0.87]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>696.48 ± 345.12</t>
+          <t>0.75 [0.70, 0.80]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>183.15 ± 174.98</t>
+          <t>0.40 [0.36, 0.43]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1022.33 ± 485.33</t>
+          <t>0.88 [0.85, 0.90]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>47.91 ± 20.02</t>
+          <t>0.48 [0.37, 0.59]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>359.98 ± 297.86</t>
+          <t>0.90 [0.87, 0.93]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>119.00 ± 122.27</t>
+          <t>0.93 [0.83, 1.00]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6044</v>
-      </c>
-      <c r="C7" t="n">
-        <v>25672</v>
-      </c>
-      <c r="D7" t="n">
-        <v>32038</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8425</v>
-      </c>
-      <c r="F7" t="n">
-        <v>47027</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1533</v>
-      </c>
-      <c r="H7" t="n">
-        <v>16559</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2618</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>208.41 ± 83.13</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>558.09 ± 298.19</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>696.48 ± 345.12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>183.15 ± 174.98</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1022.33 ± 485.33</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>47.91 ± 20.02</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>359.98 ± 297.86</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>119.00 ± 122.27</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>6044</v>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>25672</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>32038</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>8425</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>47027</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>1533</v>
       </c>
       <c r="H8" t="n">
-        <v>46</v>
+        <v>16559</v>
       </c>
       <c r="I8" t="n">
-        <v>22</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n_total</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
         <v>46</v>
@@ -779,12 +795,43 @@
         <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H9" t="n">
         <v>46</v>
       </c>
       <c r="I9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>46</v>
+      </c>
+      <c r="C10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D10" t="n">
+        <v>46</v>
+      </c>
+      <c r="E10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F10" t="n">
+        <v>46</v>
+      </c>
+      <c r="G10" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" t="n">
+        <v>46</v>
+      </c>
+      <c r="I10" t="n">
         <v>46</v>
       </c>
     </row>
@@ -799,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,42 +899,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.84]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.84]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.84]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.84]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.84]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.84]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.84]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.84]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
     </row>
@@ -899,259 +946,275 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.08 [0.02, 0.15]</t>
+          <t>0.08 [0.01, 0.16]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.79 [0.73, 0.84]</t>
+          <t>0.79 [0.72, 0.85]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.79 [0.75, 0.83]</t>
+          <t>0.79 [0.74, 0.84]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.38 [0.34, 0.43]</t>
+          <t>0.38 [0.33, 0.44]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.84 [0.81, 0.87]</t>
+          <t>0.84 [0.81, 0.88]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.62 [0.53, 0.70]</t>
+          <t>0.62 [0.52, 0.72]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.93 [0.91, 0.96]</t>
+          <t>0.93 [0.90, 0.97]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.89 [0.84, 0.94]</t>
+          <t>0.89 [0.83, 0.95]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.73 [0.37, 1.00]</t>
+          <t>0.70 [0.65, 0.75]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.72 [0.64, 0.79]</t>
+          <t>0.70 [0.65, 0.75]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.87 [0.82, 0.91]</t>
+          <t>0.70 [0.65, 0.75]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.31 [0.27, 0.35]</t>
+          <t>0.70 [0.65, 0.75]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.90]</t>
+          <t>0.70 [0.65, 0.75]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.65 [0.58, 0.72]</t>
+          <t>0.70 [0.65, 0.75]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.90 [0.86, 0.95]</t>
+          <t>0.70 [0.65, 0.75]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.96 [0.93, 0.98]</t>
+          <t>0.70 [0.65, 0.75]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.08 [0.01, 0.15]</t>
+          <t>0.73 [0.27, 1.00]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.95 [0.91, 0.99]</t>
+          <t>0.72 [0.63, 0.80]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.74 [0.70, 0.79]</t>
+          <t>0.87 [0.82, 0.92]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.58 [0.53, 0.62]</t>
+          <t>0.31 [0.26, 0.36]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.84 [0.81, 0.86]</t>
+          <t>0.86 [0.82, 0.91]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.71 [0.60, 0.81]</t>
+          <t>0.65 [0.57, 0.74]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.97 [0.96, 0.98]</t>
+          <t>0.90 [0.85, 0.95]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.85 [0.78, 0.92]</t>
+          <t>0.96 [0.93, 0.99]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>474.84 ± 292.51</t>
+          <t>0.08 [0.00, 0.17]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2200.17 ± 2043.18</t>
+          <t>0.95 [0.91, 1.00]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>817.19 ± 625.87</t>
+          <t>0.74 [0.69, 0.80]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>209.32 ± 199.02</t>
+          <t>0.58 [0.52, 0.63]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1113.29 ± 781.77</t>
+          <t>0.84 [0.80, 0.87]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>126.69 ± 85.01</t>
+          <t>0.71 [0.58, 0.83]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>345.75 ± 571.00</t>
+          <t>0.97 [0.96, 0.99]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>650.47 ± 856.37</t>
+          <t>0.85 [0.77, 0.93]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>11871</v>
-      </c>
-      <c r="C7" t="n">
-        <v>66005</v>
-      </c>
-      <c r="D7" t="n">
-        <v>25333</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6489</v>
-      </c>
-      <c r="F7" t="n">
-        <v>34512</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3674</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6915</v>
-      </c>
-      <c r="I7" t="n">
-        <v>12359</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>474.84 ± 292.51</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2200.17 ± 2043.18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>817.19 ± 625.87</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>209.32 ± 199.02</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1113.29 ± 781.77</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>126.69 ± 85.01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>345.75 ± 571.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>650.47 ± 856.37</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>11871</v>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>66005</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>25333</v>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>6489</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>34512</v>
       </c>
       <c r="G8" t="n">
-        <v>29</v>
+        <v>3674</v>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>6915</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>12359</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n_total</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
         <v>31</v>
@@ -1163,12 +1226,43 @@
         <v>31</v>
       </c>
       <c r="G9" t="n">
+        <v>29</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>31</v>
       </c>
-      <c r="H9" t="n">
+      <c r="C10" t="n">
         <v>31</v>
       </c>
-      <c r="I9" t="n">
+      <c r="D10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E10" t="n">
+        <v>31</v>
+      </c>
+      <c r="F10" t="n">
+        <v>31</v>
+      </c>
+      <c r="G10" t="n">
+        <v>31</v>
+      </c>
+      <c r="H10" t="n">
+        <v>31</v>
+      </c>
+      <c r="I10" t="n">
         <v>31</v>
       </c>
     </row>
@@ -1183,7 +1277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,42 +1330,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.78 [0.75, 0.82]</t>
+          <t>0.78 [0.74, 0.82]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.78 [0.75, 0.82]</t>
+          <t>0.78 [0.74, 0.82]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78 [0.75, 0.82]</t>
+          <t>0.78 [0.74, 0.82]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.78 [0.75, 0.82]</t>
+          <t>0.78 [0.74, 0.82]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.78 [0.75, 0.82]</t>
+          <t>0.78 [0.74, 0.82]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.78 [0.75, 0.82]</t>
+          <t>0.78 [0.74, 0.82]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.78 [0.75, 0.82]</t>
+          <t>0.78 [0.74, 0.82]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.78 [0.75, 0.82]</t>
+          <t>0.78 [0.74, 0.82]</t>
         </is>
       </c>
     </row>
@@ -1283,32 +1377,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.05 [0.00, 0.14]</t>
+          <t>0.05 [0.00, 0.16]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.82 [0.79, 0.85]</t>
+          <t>0.82 [0.78, 0.86]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.83 [0.81, 0.85]</t>
+          <t>0.83 [0.80, 0.86]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.29 [0.23, 0.34]</t>
+          <t>0.29 [0.22, 0.36]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.86 [0.77, 0.95]</t>
+          <t>0.86 [0.76, 0.97]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.18 [0.05, 0.31]</t>
+          <t>0.18 [0.02, 0.34]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -1317,76 +1411,84 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>kappa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.78 [nan, nan]</t>
+          <t>0.69 [0.64, 0.74]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.71 [0.66, 0.77]</t>
+          <t>0.69 [0.64, 0.74]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.90 [0.89, 0.92]</t>
+          <t>0.69 [0.64, 0.74]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.20 [0.15, 0.24]</t>
+          <t>0.69 [0.64, 0.74]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.96 [0.96, 0.97]</t>
+          <t>0.69 [0.64, 0.74]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.23 [0.05, 0.40]</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>0.69 [0.64, 0.74]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.69 [0.64, 0.74]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.69 [0.64, 0.74]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.06 [0.00, 0.16]</t>
+          <t>0.78 [nan, nan]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 0.99]</t>
+          <t>0.71 [0.65, 0.78]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.80]</t>
+          <t>0.90 [0.89, 0.92]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.67 [0.61, 0.73]</t>
+          <t>0.20 [0.14, 0.25]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.82 [0.74, 0.91]</t>
+          <t>0.96 [0.96, 0.97]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.26 [0.10, 0.41]</t>
+          <t>0.23 [0.01, 0.44]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1395,37 +1497,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>240.53 ± 82.52</t>
+          <t>0.06 [0.00, 0.18]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>540.89 ± 196.99</t>
+          <t>0.98 [0.97, 0.99]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>471.17 ± 165.70</t>
+          <t>0.77 [0.73, 0.81]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>68.61 ± 41.62</t>
+          <t>0.67 [0.60, 0.74]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1204.28 ± 235.97</t>
+          <t>0.82 [0.72, 0.93]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14.69 ± 12.74</t>
+          <t>0.26 [0.07, 0.44]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1434,26 +1536,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4089</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9736</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8481</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1235</v>
-      </c>
-      <c r="F7" t="n">
-        <v>21677</v>
-      </c>
-      <c r="G7" t="n">
-        <v>191</v>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>240.53 ± 82.52</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>540.89 ± 196.99</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>471.17 ± 165.70</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>68.61 ± 41.62</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1204.28 ± 235.97</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>14.69 ± 12.74</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -1461,26 +1575,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>support_total</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>4089</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>9736</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>8481</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>1235</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>21677</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>191</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -1488,11 +1602,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n_total</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>18</v>
@@ -1507,10 +1621,37 @@
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/ntnu_datasets.xlsx
+++ b/results/ntnu_datasets.xlsx
@@ -8,8 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Children" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Adults" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Older Adults" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Children matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Adults" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Adults matrix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Older Adults" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Older Adults matrix" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -846,424 +849,2166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>lie</t>
+          <t>pred</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>sit</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>n_total</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>sum</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>walk</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>stairs</t>
+          <t>std</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>lower</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>upper</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.81 [0.78, 0.85]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.81 [0.78, 0.85]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.81 [0.78, 0.85]</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.81 [0.78, 0.85]</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.81 [0.78, 0.85]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.81 [0.78, 0.85]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.81 [0.78, 0.85]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.81 [0.78, 0.85]</t>
-        </is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.42911911201934</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9285963232736065</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2124498520473197</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8344013358244373</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fscore</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.08 [0.01, 0.16]</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.79 [0.72, 0.85]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.79 [0.74, 0.84]</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.38 [0.33, 0.44]</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.84 [0.81, 0.88]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.62 [0.52, 0.72]</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.93 [0.90, 0.97]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.89 [0.83, 0.95]</t>
-        </is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.00303030303030303</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01421338109037403</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.009332163165841453</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kappa</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.70 [0.65, 0.75]</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.70 [0.65, 0.75]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.70 [0.65, 0.75]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.70 [0.65, 0.75]</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.70 [0.65, 0.75]</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.70 [0.65, 0.75]</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.70 [0.65, 0.75]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.70 [0.65, 0.75]</t>
-        </is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.73 [0.27, 1.00]</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.72 [0.63, 0.80]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.87 [0.82, 0.92]</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.31 [0.26, 0.36]</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.86 [0.82, 0.91]</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.65 [0.57, 0.74]</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.90 [0.85, 0.95]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.96 [0.93, 0.99]</t>
-        </is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4585187547097334</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02084176157771515</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.07410733883340473</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05369911489678965</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.08 [0.00, 0.17]</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.95 [0.91, 1.00]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.74 [0.69, 0.80]</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.58 [0.52, 0.63]</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.84 [0.80, 0.87]</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.71 [0.58, 0.83]</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.97 [0.96, 0.99]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.85 [0.77, 0.93]</t>
-        </is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" t="n">
+        <v>46</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4869875222816399</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.02213579646734727</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0561152877121841</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.04701592121593207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>474.84 ± 292.51</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2200.17 ± 2043.18</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>817.19 ± 625.87</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>209.32 ± 199.02</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1113.29 ± 781.77</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>126.69 ± 85.01</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>345.75 ± 571.00</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>650.47 ± 856.37</t>
-        </is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" t="n">
+        <v>46</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01590909090909091</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.07462025072446365</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.04899385662066762</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>support_total</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>11871</v>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>66005</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>25333</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>6489</v>
+        <v>0.2087079443226152</v>
       </c>
       <c r="F8" t="n">
-        <v>34512</v>
+        <v>0.009486724741937055</v>
       </c>
       <c r="G8" t="n">
-        <v>3674</v>
+        <v>0.02403702180538541</v>
       </c>
       <c r="H8" t="n">
-        <v>6915</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>12359</v>
+        <v>0.02014414316541225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>25</v>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>n_total</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>31</v>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>31</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D11" t="n">
+        <v>46</v>
+      </c>
+      <c r="E11" t="n">
+        <v>27.78502893294327</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9581044459635611</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1219730435878126</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9117083814901461</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>29</v>
+      </c>
+      <c r="D12" t="n">
+        <v>46</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>29</v>
+      </c>
+      <c r="D13" t="n">
+        <v>46</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.01831251645255918</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0006314660845710062</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.002059111924980067</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.001414710372154715</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>29</v>
+      </c>
+      <c r="D14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.164425126207867</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.04015259055889196</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1225274870064034</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.08675955402965209</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>29</v>
+      </c>
+      <c r="D15" t="n">
+        <v>46</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D16" t="n">
+        <v>46</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D17" t="n">
+        <v>46</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0322334243963014</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.00111149739297591</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.002572959029169574</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0001327961201912839</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.002090198665760537</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>46</v>
+      </c>
+      <c r="D18" t="n">
+        <v>46</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>46</v>
+      </c>
+      <c r="D19" t="n">
+        <v>46</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.02219945355191257</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0004825968163459254</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.003073834654053165</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.001395413032748164</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>46</v>
+      </c>
+      <c r="D20" t="n">
+        <v>46</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41.44945517513595</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9010751125029554</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.09095915432766315</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8740635779068955</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9280866470990152</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D21" t="n">
+        <v>46</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.690672723099164</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.03675375484998183</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.04295892257211588</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02399652956745456</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.04951098013250911</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>46</v>
+      </c>
+      <c r="D22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1744499828459329</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.003792390931433323</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.01076562517953916</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0005953948826596359</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.00698938698020701</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>46</v>
+      </c>
+      <c r="D23" t="n">
+        <v>46</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1756773765767205</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.00381907340384175</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.01182264423798859</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0003081814412697749</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.007329965366413725</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>46</v>
+      </c>
+      <c r="D24" t="n">
+        <v>46</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.054356104558134</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.02292078488169857</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0418629531143631</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0104890223537795</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.03535254740961764</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>46</v>
+      </c>
+      <c r="D25" t="n">
+        <v>46</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.433189184232186</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.03115628661374318</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.03796803161249768</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.01988117299790155</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.04243140022958482</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>46</v>
+      </c>
+      <c r="D26" t="n">
+        <v>46</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.01836437677952404</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0003992255821635662</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.001251267378221464</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.764503784587246e-05</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.0007708061264812599</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>46</v>
+      </c>
+      <c r="D27" t="n">
+        <v>46</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.3373827062147183</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.007334406656841702</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.01299657764260323</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.003474899505324692</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.01119391380835871</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>46</v>
+      </c>
+      <c r="D28" t="n">
+        <v>46</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.110705161683796</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.06762402525399555</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.07615862346601854</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.04500770578899568</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.09024034471899542</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>46</v>
+      </c>
+      <c r="D29" t="n">
+        <v>46</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18.1821694825286</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3952645539680131</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1287195210850286</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3570395746058305</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4334895333301957</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>46</v>
+      </c>
+      <c r="D30" t="n">
+        <v>46</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7823194305071083</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.01700694414145888</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.022456725646675</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.01033811980812945</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.0236757684747883</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>46</v>
+      </c>
+      <c r="D31" t="n">
+        <v>46</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.086696386795366</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.02362383449555143</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.02739230879123077</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.01548932288922202</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.03175834610188085</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>46</v>
+      </c>
+      <c r="D32" t="n">
+        <v>46</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.842171561785236</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2139602513431573</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.130927319362508</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1750796368225999</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.2528408658637147</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>46</v>
+      </c>
+      <c r="D33" t="n">
+        <v>46</v>
+      </c>
+      <c r="E33" t="n">
+        <v>12.64019089370565</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.2747867585588183</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1178391134061078</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2397928614402074</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3097806556774293</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>46</v>
+      </c>
+      <c r="D34" t="n">
+        <v>46</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.3775006306749611</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.008206535449455677</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.01523257792362533</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.003683018178296874</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.01273005272061448</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>46</v>
+      </c>
+      <c r="D35" t="n">
+        <v>46</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.77395628647646</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.16899904970601</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.2421220057887304</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.09709768931879409</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2409004100932259</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>46</v>
+      </c>
+      <c r="D36" t="n">
+        <v>46</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.04936824843834853</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.001073222792138011</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.004048560478474765</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.002275496848409696</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>46</v>
+      </c>
+      <c r="D37" t="n">
+        <v>46</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5307594445334815</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.01153824879420612</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.01253984260747502</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.007814375205839401</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.01526212238257284</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>46</v>
+      </c>
+      <c r="D38" t="n">
+        <v>46</v>
+      </c>
+      <c r="E38" t="n">
+        <v>36.53074361178548</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.7941466002562061</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.2472957418085188</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.7207088299218839</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8675843705905283</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>46</v>
+      </c>
+      <c r="D39" t="n">
+        <v>46</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.03872157161673516</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0008417732960159817</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.003691619049531162</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.001938048832095347</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>46</v>
+      </c>
+      <c r="D40" t="n">
+        <v>46</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.4164867282452374</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.009054059309679074</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.01777289056916365</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.003776162301626675</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.01433195631773147</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>46</v>
+      </c>
+      <c r="D41" t="n">
+        <v>46</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2824634782292873</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.006140510396288854</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.006729612763590792</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.004142062089183879</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.008138958703393829</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>32</v>
+      </c>
+      <c r="D42" t="n">
+        <v>46</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>32</v>
+      </c>
+      <c r="D43" t="n">
+        <v>46</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>32</v>
+      </c>
+      <c r="D44" t="n">
+        <v>46</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.985811120309127</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.1245565975096602</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.1821462193517442</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.0588858824454551</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1902273125738653</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>32</v>
+      </c>
+      <c r="D45" t="n">
+        <v>46</v>
+      </c>
+      <c r="E45" t="n">
+        <v>7.93294682345218</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2479045882328806</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.2433258009225188</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.1601762818369389</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.3356328946288224</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>32</v>
+      </c>
+      <c r="D46" t="n">
+        <v>46</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.09779367918902802</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.003056052474657126</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0120406806406054</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.007397180774450828</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>32</v>
+      </c>
+      <c r="D47" t="n">
+        <v>46</v>
+      </c>
+      <c r="E47" t="n">
+        <v>15.38315468130243</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.4807235837907011</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.2996056386299306</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.3727042321065457</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.5887429354748565</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>32</v>
+      </c>
+      <c r="D48" t="n">
+        <v>46</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.7460366744883993</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.02331364607776248</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.03467917888110968</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.01081046877840809</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.03581682337711686</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>32</v>
+      </c>
+      <c r="D49" t="n">
+        <v>46</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.854257021258832</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.1204455319143385</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.139069653015201</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.07030557518208978</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1705854886465872</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>46</v>
+      </c>
+      <c r="D50" t="n">
+        <v>46</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.01249552136654558</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.0002716417688379475</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0009868174891460183</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.0005646903898931011</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>46</v>
+      </c>
+      <c r="D51" t="n">
+        <v>46</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.1270341589126501</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.002761612150275003</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.004620694640057216</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.001389435220417872</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.004133789080132134</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>46</v>
+      </c>
+      <c r="D52" t="n">
+        <v>46</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7267796067929644</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.01579955666941227</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.01707280980081607</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.01072955798708678</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.02086955535173775</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>46</v>
+      </c>
+      <c r="D53" t="n">
+        <v>46</v>
+      </c>
+      <c r="E53" t="n">
+        <v>5.875940471294936</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.1277378363324986</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.08433902303375547</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1026922380602493</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1527834346047479</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>46</v>
+      </c>
+      <c r="D54" t="n">
+        <v>46</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.3973064841848469</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.008637097482279281</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.01608569996812178</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.003860234236326508</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.01341396072823205</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>46</v>
+      </c>
+      <c r="D55" t="n">
+        <v>46</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.4052426007160604</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.008809621754696966</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.01307424393051042</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.004927050562641549</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.01269219294675238</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>46</v>
+      </c>
+      <c r="D56" t="n">
+        <v>46</v>
+      </c>
+      <c r="E56" t="n">
+        <v>34.58336535140028</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.7518122902478322</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.1579885546363571</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.7048954808196295</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.798729099676035</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>46</v>
+      </c>
+      <c r="D57" t="n">
+        <v>46</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3.852255735377151</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.08374468989950327</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.06825947627663302</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.06347412759509483</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.1040152522039117</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>46</v>
+      </c>
+      <c r="D58" t="n">
+        <v>46</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>46</v>
+      </c>
+      <c r="D59" t="n">
+        <v>46</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.1689733570167263</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.003673333848189702</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.00657606361092027</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.00172048401086177</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.005626183685517633</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>46</v>
+      </c>
+      <c r="D60" t="n">
+        <v>46</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.540040326121489</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.0334791375243802</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.03910884064433324</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.02186524544408716</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.04509302960467323</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>46</v>
+      </c>
+      <c r="D61" t="n">
+        <v>46</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.826264555884017</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.03970140338878297</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.02940813327588939</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.0309682658034697</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.04843454097409625</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>46</v>
+      </c>
+      <c r="D62" t="n">
+        <v>46</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.5798779361670832</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.01260604209058877</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.01303647229379096</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.008734687690065095</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.01647739649111243</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>46</v>
+      </c>
+      <c r="D63" t="n">
+        <v>46</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9590180177447236</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.02084821777705921</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.05060219749165498</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.005821220018717061</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.03587521553540135</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>46</v>
+      </c>
+      <c r="D64" t="n">
+        <v>46</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6079598046860382</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.01321651749317474</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.01043179896886345</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.01011865559208954</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.01631437939425994</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>46</v>
+      </c>
+      <c r="D65" t="n">
+        <v>46</v>
+      </c>
+      <c r="E65" t="n">
+        <v>40.31786600237992</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.8764753478778244</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.07620292408577729</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.8538458727526594</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.8991048230029894</v>
       </c>
     </row>
   </sheetData>
@@ -1330,42 +3075,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.81 [0.78, 0.85]</t>
         </is>
       </c>
     </row>
@@ -1377,6 +3122,2610 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>0.08 [0.01, 0.16]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.79 [0.72, 0.85]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.79 [0.74, 0.84]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.38 [0.33, 0.44]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.84 [0.81, 0.88]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.62 [0.52, 0.72]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.93 [0.90, 0.97]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.89 [0.83, 0.95]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.70 [0.65, 0.75]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.70 [0.65, 0.75]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.70 [0.65, 0.75]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.70 [0.65, 0.75]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.70 [0.65, 0.75]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.70 [0.65, 0.75]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.70 [0.65, 0.75]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.70 [0.65, 0.75]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.73 [0.27, 1.00]</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.72 [0.63, 0.80]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.87 [0.82, 0.92]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.31 [0.26, 0.36]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.86 [0.82, 0.91]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.65 [0.57, 0.74]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.90 [0.85, 0.95]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.96 [0.93, 0.99]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.08 [0.00, 0.17]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.95 [0.91, 1.00]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.74 [0.69, 0.80]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.58 [0.52, 0.63]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.84 [0.80, 0.87]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.71 [0.58, 0.83]</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.97 [0.96, 0.99]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.85 [0.77, 0.93]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>474.84 ± 292.51</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2200.17 ± 2043.18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>817.19 ± 625.87</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>209.32 ± 199.02</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1113.29 ± 781.77</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>126.69 ± 85.01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>345.75 ± 571.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>650.47 ± 856.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>support_total</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11871</v>
+      </c>
+      <c r="C8" t="n">
+        <v>66005</v>
+      </c>
+      <c r="D8" t="n">
+        <v>25333</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6489</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34512</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3674</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6915</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12359</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" t="n">
+        <v>31</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G9" t="n">
+        <v>29</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>31</v>
+      </c>
+      <c r="C10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E10" t="n">
+        <v>31</v>
+      </c>
+      <c r="F10" t="n">
+        <v>31</v>
+      </c>
+      <c r="G10" t="n">
+        <v>31</v>
+      </c>
+      <c r="H10" t="n">
+        <v>31</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.20128091496537</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8526989955244934</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1707353007931282</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7704072147033262</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9349907763456605</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>31</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05800883215332904</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.003053096429122581</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.009180714226198402</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.007478059043031524</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>31</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6882022388879362</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03622117046778611</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04075542494289004</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.01657768443359146</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05586465650198076</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2845162899829668</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01497454157805088</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03138451094449853</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.03010139164260498</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>31</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.295872278232148</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.06820380411748148</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1178195284737383</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.01141660915208998</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.124990999082873</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3698501241667016</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01946579600877377</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.04847236485507495</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0428287280211208</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>19</v>
+      </c>
+      <c r="D9" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1022693216115456</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005382595874291875</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.006762339629952767</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002123252504284098</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.008641939244299651</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>31</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.99724433062674</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0798897732250696</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2184175326155469</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1700480995049835</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" t="n">
+        <v>31</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.29028854758506</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0116115419034024</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01907095311789614</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.00373943936162213</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01948364444518266</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" t="n">
+        <v>31</v>
+      </c>
+      <c r="E14" t="n">
+        <v>22.70106027768173</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9080424111072694</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2217069726284625</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8165262707251119</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9995585514894268</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>31</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>31</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>31</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.01140684410646388</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0004562737642585551</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.002281368821292775</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.001397976530020391</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>31</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" t="n">
+        <v>31</v>
+      </c>
+      <c r="E20" t="n">
+        <v>19.41652497158246</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9708262485791229</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.03329226488113525</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9552449889924036</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9864075081658422</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>31</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2012776002688419</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0100638800134421</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.01920938351073076</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.001073611791974851</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.01905414823490934</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="n">
+        <v>31</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="n">
+        <v>31</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.001461988304093567</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7.309941520467836e-05</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.000326910523026285</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0002260982495912506</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="n">
+        <v>31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.03840858943298806</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.001920429471649403</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005505393661785239</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.004497033018377809</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" t="n">
+        <v>31</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3423268504116201</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.01711634252058101</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.02175982983579709</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.006932428676181976</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.02730025636498004</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>31</v>
+      </c>
+      <c r="D26" t="n">
+        <v>31</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1052545913066171</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.003395309396987648</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.009413084165351793</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.006848056544133787</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>31</v>
+      </c>
+      <c r="D27" t="n">
+        <v>31</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.002610966057441253</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.422471153036302e-05</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0004689433473283941</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.0002562345200287407</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>31</v>
+      </c>
+      <c r="D28" t="n">
+        <v>31</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1375495121828079</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.004437081038155093</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.008176751298000664</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.001437824447949075</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.00743633762836111</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>31</v>
+      </c>
+      <c r="D29" t="n">
+        <v>31</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.85185380833014</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5758662518816173</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1398708840799325</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5245611973965609</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6271713063666737</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>31</v>
+      </c>
+      <c r="D30" t="n">
+        <v>31</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.3401082783940269</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.01097123478690409</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.02118277426015394</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.003201330458989931</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.01874113911481825</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>31</v>
+      </c>
+      <c r="D31" t="n">
+        <v>31</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.515819825255375</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0488974137179153</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.06878290293429819</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.02366764123240049</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.07412718620343012</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>31</v>
+      </c>
+      <c r="D32" t="n">
+        <v>31</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4.897283478754927</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1579768864114493</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1122724292163547</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1167950268986221</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1991587459242765</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>31</v>
+      </c>
+      <c r="D33" t="n">
+        <v>31</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.149519539718669</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1983715980554409</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1327780119875602</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1496682300582367</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2470749660526451</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>30</v>
+      </c>
+      <c r="D34" t="n">
+        <v>31</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.4530678292201228</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.01510226097400409</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.05694271447788889</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.0363650200037121</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" t="n">
+        <v>31</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.08487958941966048</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.002829319647322016</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.01549682193230829</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.008615928057093448</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>30</v>
+      </c>
+      <c r="D36" t="n">
+        <v>31</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>30</v>
+      </c>
+      <c r="D37" t="n">
+        <v>31</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6014461866513275</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.02004820622171092</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.05574497076908215</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.04086372040028709</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>30</v>
+      </c>
+      <c r="D38" t="n">
+        <v>31</v>
+      </c>
+      <c r="E38" t="n">
+        <v>28.51377329282768</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9504591097609226</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.120634351694573</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9054135025343342</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9955047169875111</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" t="n">
+        <v>31</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.01363193768257059</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0004543979227523531</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.002488839923749538</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.001383746023688992</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" t="n">
+        <v>31</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.3116442613831799</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.010388142046106</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.04208755704292787</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.02610389412709185</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>30</v>
+      </c>
+      <c r="D41" t="n">
+        <v>31</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.02155690281545929</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0007185634271819764</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.001231027921418992</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0002588900468035567</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.001178236807560396</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>29</v>
+      </c>
+      <c r="D42" t="n">
+        <v>31</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.225420926416761</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.04225589401437108</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.1724794020569384</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1078635497945485</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>29</v>
+      </c>
+      <c r="D43" t="n">
+        <v>31</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>29</v>
+      </c>
+      <c r="D44" t="n">
+        <v>31</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6737486626012527</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.02323271250349147</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.06653609616590385</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.0485416899358712</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>29</v>
+      </c>
+      <c r="D45" t="n">
+        <v>31</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.931351307662053</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.06659832095386391</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.09843972026326031</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.02915385393282847</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.1040427879748993</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>29</v>
+      </c>
+      <c r="D46" t="n">
+        <v>31</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>29</v>
+      </c>
+      <c r="D47" t="n">
+        <v>31</v>
+      </c>
+      <c r="E47" t="n">
+        <v>20.47400287019498</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.7060000989722408</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.321427146866539</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5837357511223863</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.8282644468220953</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>29</v>
+      </c>
+      <c r="D48" t="n">
+        <v>31</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.2435535146591311</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.008398397057211416</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.04328326128960313</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.02486246913692748</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>29</v>
+      </c>
+      <c r="D49" t="n">
+        <v>31</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.451922718465823</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.1535145764988215</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.2536549882210088</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.05702937910327856</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2499997738943644</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>31</v>
+      </c>
+      <c r="D50" t="n">
+        <v>31</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.07434874857665132</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.002398346728279075</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.01110213651179608</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.006470643277950718</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>31</v>
+      </c>
+      <c r="D51" t="n">
+        <v>31</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.01301818257357458</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.0004199413733411155</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.002196335662688448</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.001225563798500792</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>31</v>
+      </c>
+      <c r="D52" t="n">
+        <v>31</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.03529845586171755</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.001138659866507018</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.004421229351924983</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.002760379885534091</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>31</v>
+      </c>
+      <c r="D53" t="n">
+        <v>31</v>
+      </c>
+      <c r="E53" t="n">
+        <v>5.244868196145869</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.1691892966498667</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.1105063637006991</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1286552351980936</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.2097233581016399</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>31</v>
+      </c>
+      <c r="D54" t="n">
+        <v>31</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5710649644128943</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.01842145046493207</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.05061632599295416</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.03698766873104273</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>31</v>
+      </c>
+      <c r="D55" t="n">
+        <v>31</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.1448013682977464</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.004671011880572466</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.009266741829836564</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.001271943535461986</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.008070080225682945</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>31</v>
+      </c>
+      <c r="D56" t="n">
+        <v>31</v>
+      </c>
+      <c r="E56" t="n">
+        <v>23.03742498350323</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.7431427414033298</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.1432864540681305</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.6905848457319557</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.795700637074704</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>31</v>
+      </c>
+      <c r="D57" t="n">
+        <v>31</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.879175100628323</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.06061855163317171</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.06158267477633991</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.03802984415828327</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.08320725910806015</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>31</v>
+      </c>
+      <c r="D58" t="n">
+        <v>31</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.04613298601540699</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.001488160839206677</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.005906376719516639</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.003654637310685172</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>31</v>
+      </c>
+      <c r="D59" t="n">
+        <v>31</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.004008016032064128</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0001292908397440041</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0007198609299670337</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.0003933379606052412</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>31</v>
+      </c>
+      <c r="D60" t="n">
+        <v>31</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.2398560073134023</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.007737290558496848</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.01532295239320369</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.002116786244275318</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.01335779487271838</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>31</v>
+      </c>
+      <c r="D61" t="n">
+        <v>31</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3.283726509254223</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.1059266615888459</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.08370481213813216</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.0752234886185936</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.1366298345590982</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>31</v>
+      </c>
+      <c r="D62" t="n">
+        <v>31</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.1126680075516603</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.003634451856505171</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.004478237840531332</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.001991820955036058</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.005277082757974283</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>31</v>
+      </c>
+      <c r="D63" t="n">
+        <v>31</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7870045245643215</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.02538724272788134</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.02467041407200153</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.01633806178891182</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.03443642366685085</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>31</v>
+      </c>
+      <c r="D64" t="n">
+        <v>31</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6398074359218365</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.02063894954586569</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.01916779383403519</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.01360814600528384</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.02766975308644754</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>31</v>
+      </c>
+      <c r="D65" t="n">
+        <v>31</v>
+      </c>
+      <c r="E65" t="n">
+        <v>25.88679651334709</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.8350579520434545</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.09805822056876318</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.7990899063555967</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.8710259977313122</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.78 [0.74, 0.82]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.78 [0.74, 0.82]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.78 [0.74, 0.82]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.78 [0.74, 0.82]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.78 [0.74, 0.82]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.78 [0.74, 0.82]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.78 [0.74, 0.82]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.78 [0.74, 0.82]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fscore</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>0.05 [0.00, 0.16]</t>
         </is>
       </c>
@@ -1463,7 +5812,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.78 [nan, nan]</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1596,8 +5945,12 @@
       <c r="G8" t="n">
         <v>191</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1623,8 +5976,12 @@
       <c r="G9" t="n">
         <v>13</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1650,8 +6007,1657 @@
       <c r="G10" t="n">
         <v>18</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>18</v>
+      </c>
+      <c r="I10" t="n">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.242535625036333</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1835238411306621</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1552504234114537</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.00913237784773257</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005797552837851999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.006151551233173906</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01211320446229124</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15.84474957658855</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9320440927405027</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2402406997153185</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8085237227429884</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>17</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.008849557522123894</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0004916420845624386</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.002085860711464741</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001528916213290715</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12.06543987482939</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6703022152682993</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1405781904514687</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6003943258213822</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7402101047152163</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3063306832056832</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.01701837128920462</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.03752584802705606</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.03567953648739301</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.056629531970461</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2253683073316922</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1042199798015807</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1735409306758227</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2771956839875618</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.562750352472345</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.08681946402624137</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1017874907343491</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.03620173572511832</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1374371923273644</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1207482993197279</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.006708238851095994</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0284606470885742</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.02086138567896499</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D21" t="n">
+        <v>18</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2122057276470469</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.01178920709150261</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.006786697454523753</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.008414261846889355</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.01516415233611586</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" t="n">
+        <v>18</v>
+      </c>
+      <c r="E22" t="n">
+        <v>17.64273721371823</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9801520674287906</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.02948894528163316</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.965487559939869</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.9948165749177121</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.007145763415129248</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0003969868563960693</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0009348583566682196</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0008618809799909409</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>18</v>
+      </c>
+      <c r="D25" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.01716299589986272</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0009534997722145956</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.001207915467162209</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0003528175421445703</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.001554182002284621</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.06570512820512821</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.2369032088045249</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2088643045133916</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>13</v>
+      </c>
+      <c r="D27" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>13</v>
+      </c>
+      <c r="D28" t="n">
+        <v>18</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>13</v>
+      </c>
+      <c r="D29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.383459595959596</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3371891996891997</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2174732764476325</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.205771413993476</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4686069853849233</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>13</v>
+      </c>
+      <c r="D30" t="n">
+        <v>18</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>13</v>
+      </c>
+      <c r="D31" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.315079365079365</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.255006105006105</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3120342139873191</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.06644571665239618</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4435664933598139</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>13</v>
+      </c>
+      <c r="D32" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7119047619047618</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.05476190476190475</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1263700429496724</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1311265574401315</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>13</v>
+      </c>
+      <c r="D33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.73538961038961</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.2873376623376623</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.3660621297328293</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.06612853125560353</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5085467934197212</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>18</v>
+      </c>
+      <c r="D34" t="n">
+        <v>18</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.01636904761904762</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0009093915343915344</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.00385822152433136</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.002828039960000535</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>18</v>
+      </c>
+      <c r="D35" t="n">
+        <v>18</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>18</v>
+      </c>
+      <c r="D36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>18</v>
+      </c>
+      <c r="D37" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.914091351916052</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.1618939639953362</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0724134238601382</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.125883615495119</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1979043124955534</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>18</v>
+      </c>
+      <c r="D38" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.0001388888888888889</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0005892556509887896</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0004319188302546272</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>18</v>
+      </c>
+      <c r="D39" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.1196632869987004</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.006647960388816689</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.02308004010729743</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.01812539431416215</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>18</v>
+      </c>
+      <c r="D40" t="n">
+        <v>18</v>
+      </c>
+      <c r="E40" t="n">
+        <v>13.87501467578211</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.7708341486545618</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.08149211291501537</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.7303090743015432</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8113592230075803</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>18</v>
+      </c>
+      <c r="D41" t="n">
+        <v>18</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.07236163768409</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.05957564653800498</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.03205784357997013</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.04363365597959899</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.07551763709641097</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>18</v>
+      </c>
+      <c r="D42" t="n">
+        <v>18</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.1186113789778206</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.006589521054323369</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0279569701337015</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.02049219522519543</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>lie</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>18</v>
+      </c>
+      <c r="D43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D44" t="n">
+        <v>18</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.002371541501976285</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0001317523056653492</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.000558977692637587</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.0004097253725735594</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>shuffle</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>18</v>
+      </c>
+      <c r="D45" t="n">
+        <v>18</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.719518523357016</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.09552880685316756</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.05992118771571776</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.06573070123731455</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.1253269124690206</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>18</v>
+      </c>
+      <c r="D46" t="n">
+        <v>18</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.008488585614578778</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.000471588089698821</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0007970715653356633</v>
+      </c>
+      <c r="H46" t="n">
+        <v>7.521372542641086e-05</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.0008679624539712312</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>stairs</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>18</v>
+      </c>
+      <c r="D47" t="n">
+        <v>18</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9570043253098853</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.05316690696166029</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.1816465806156674</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.1434976263663496</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>18</v>
+      </c>
+      <c r="D48" t="n">
+        <v>18</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.3554925037092719</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.01974958353940399</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.01343656374934449</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.01306773758507079</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.0264314294937372</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>18</v>
+      </c>
+      <c r="D49" t="n">
+        <v>18</v>
+      </c>
+      <c r="E49" t="n">
+        <v>14.83851314152945</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.8243618411960807</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.2159421929266566</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.7169763150233484</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.931747367368813</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/ntnu_datasets.xlsx
+++ b/results/ntnu_datasets.xlsx
@@ -471,42 +471,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.85]</t>
+          <t>0.83 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.85]</t>
+          <t>0.83 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.85]</t>
+          <t>0.83 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.85]</t>
+          <t>0.83 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.85]</t>
+          <t>0.83 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.85]</t>
+          <t>0.83 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.85]</t>
+          <t>0.83 [0.80, 0.85]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.82 [0.80, 0.85]</t>
+          <t>0.83 [0.80, 0.85]</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.88 [0.86, 0.90]</t>
+          <t>0.89 [0.87, 0.90]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.45 [0.35, 0.55]</t>
+          <t>0.46 [0.36, 0.57]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.82 [0.78, 0.86]</t>
+          <t>0.83 [0.79, 0.87]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -565,42 +565,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.80]</t>
+          <t>0.78 [0.75, 0.81]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.80]</t>
+          <t>0.78 [0.75, 0.81]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.80]</t>
+          <t>0.78 [0.75, 0.81]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.80]</t>
+          <t>0.78 [0.75, 0.81]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.80]</t>
+          <t>0.78 [0.75, 0.81]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.80]</t>
+          <t>0.78 [0.75, 0.81]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.80]</t>
+          <t>0.78 [0.75, 0.81]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.77 [0.74, 0.80]</t>
+          <t>0.78 [0.75, 0.81]</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.30 [0.28, 0.33]</t>
+          <t>0.31 [0.28, 0.34]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.49 [0.39, 0.59]</t>
+          <t>0.50 [0.39, 0.60]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.76 [0.71, 0.82]</t>
+          <t>0.79 [0.74, 0.84]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.40 [0.36, 0.43]</t>
+          <t>0.39 [0.35, 0.43]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.88 [0.85, 0.90]</t>
+          <t>0.89 [0.87, 0.91]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.48 [0.37, 0.59]</t>
+          <t>0.50 [0.39, 0.61]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.90 [0.87, 0.93]</t>
+          <t>0.90 [0.87, 0.92]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1016,19 +1016,19 @@
         <v>46</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4585187547097334</v>
+        <v>0.4085187547097334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02084176157771515</v>
+        <v>0.01856903430498788</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07410733883340473</v>
+        <v>0.06354615527034002</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05369911489678965</v>
+        <v>0.04674382115680178</v>
       </c>
     </row>
     <row r="6">
@@ -1082,19 +1082,19 @@
         <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01590909090909091</v>
+        <v>0.01818181818181818</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07462025072446365</v>
+        <v>0.0852802865422442</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04899385662066762</v>
+        <v>0.05599297899504874</v>
       </c>
     </row>
     <row r="8">
@@ -1511,19 +1511,19 @@
         <v>46</v>
       </c>
       <c r="E20" t="n">
-        <v>41.44945517513595</v>
+        <v>41.25929153923031</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9010751125029554</v>
+        <v>0.8969411204180503</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09095915432766315</v>
+        <v>0.08982734462742603</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8740635779068955</v>
+        <v>0.8702656918148406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9280866470990152</v>
+        <v>0.92361654902126</v>
       </c>
     </row>
     <row r="21">
@@ -1544,19 +1544,19 @@
         <v>46</v>
       </c>
       <c r="E21" t="n">
-        <v>1.690672723099164</v>
+        <v>1.651498946937918</v>
       </c>
       <c r="F21" t="n">
-        <v>0.03675375484998183</v>
+        <v>0.03590215102038952</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04295892257211588</v>
+        <v>0.04295319417889763</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02399652956745456</v>
+        <v>0.02314662686066553</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04951098013250911</v>
+        <v>0.0486576751801135</v>
       </c>
     </row>
     <row r="22">
@@ -1610,19 +1610,19 @@
         <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1756773765767205</v>
+        <v>0.1765444432332609</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00381907340384175</v>
+        <v>0.003837922678983932</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01182264423798859</v>
+        <v>0.01202803222123091</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0003081814412697749</v>
+        <v>0.0002660380141823382</v>
       </c>
       <c r="I23" t="n">
-        <v>0.007329965366413725</v>
+        <v>0.007409807343785525</v>
       </c>
     </row>
     <row r="24">
@@ -1643,19 +1643,19 @@
         <v>46</v>
       </c>
       <c r="E24" t="n">
-        <v>1.054356104558134</v>
+        <v>1.05318924341461</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02292078488169857</v>
+        <v>0.02289541833510022</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0418629531143631</v>
+        <v>0.04187316613259563</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0104890223537795</v>
+        <v>0.01046062291513904</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03535254740961764</v>
+        <v>0.03533021375506141</v>
       </c>
     </row>
     <row r="25">
@@ -1676,19 +1676,19 @@
         <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>1.433189184232186</v>
+        <v>1.662826390786052</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03115628661374318</v>
+        <v>0.03614839979969679</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03796803161249768</v>
+        <v>0.03874382954737142</v>
       </c>
       <c r="H25" t="n">
-        <v>0.01988117299790155</v>
+        <v>0.02464290263519214</v>
       </c>
       <c r="I25" t="n">
-        <v>0.04243140022958482</v>
+        <v>0.04765389696420144</v>
       </c>
     </row>
     <row r="26">
@@ -1775,19 +1775,19 @@
         <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>3.110705161683796</v>
+        <v>3.065050272597905</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06762402525399555</v>
+        <v>0.06663152766517186</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07615862346601854</v>
+        <v>0.07595339265017804</v>
       </c>
       <c r="H28" t="n">
-        <v>0.04500770578899568</v>
+        <v>0.04407615422944446</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09024034471899542</v>
+        <v>0.08918690110089926</v>
       </c>
     </row>
     <row r="29">
@@ -1808,19 +1808,19 @@
         <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>18.1821694825286</v>
+        <v>17.94939857686568</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3952645539680131</v>
+        <v>0.3902043168883844</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1287195210850286</v>
+        <v>0.1258173184160388</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3570395746058305</v>
+        <v>0.3528411853344587</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4334895333301957</v>
+        <v>0.4275674484423101</v>
       </c>
     </row>
     <row r="30">
@@ -1841,19 +1841,19 @@
         <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7823194305071083</v>
+        <v>0.7857976913766735</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01700694414145888</v>
+        <v>0.01708255850818855</v>
       </c>
       <c r="G30" t="n">
-        <v>0.022456725646675</v>
+        <v>0.02242197568667805</v>
       </c>
       <c r="H30" t="n">
-        <v>0.01033811980812945</v>
+        <v>0.01042405363916822</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0236757684747883</v>
+        <v>0.02374106337720889</v>
       </c>
     </row>
     <row r="31">
@@ -1874,19 +1874,19 @@
         <v>46</v>
       </c>
       <c r="E31" t="n">
-        <v>1.086696386795366</v>
+        <v>1.045071679794861</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02362383449555143</v>
+        <v>0.02271894956075785</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02739230879123077</v>
+        <v>0.02631439290438121</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01548932288922202</v>
+        <v>0.01490453946025811</v>
       </c>
       <c r="I31" t="n">
-        <v>0.03175834610188085</v>
+        <v>0.03053335966125758</v>
       </c>
     </row>
     <row r="32">
@@ -1907,19 +1907,19 @@
         <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>9.842171561785236</v>
+        <v>9.945326084462156</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2139602513431573</v>
+        <v>0.2162027409665686</v>
       </c>
       <c r="G32" t="n">
-        <v>0.130927319362508</v>
+        <v>0.13184273416001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1750796368225999</v>
+        <v>0.1770502818070055</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2528408658637147</v>
+        <v>0.2553552001261317</v>
       </c>
     </row>
     <row r="33">
@@ -1940,19 +1940,19 @@
         <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>12.64019089370565</v>
+        <v>12.85360861190847</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2747867585588183</v>
+        <v>0.2794262741719233</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1178391134061078</v>
+        <v>0.1170734315123229</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2397928614402074</v>
+        <v>0.2446597565085901</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3097806556774293</v>
+        <v>0.3141927918352565</v>
       </c>
     </row>
     <row r="34">
@@ -2072,19 +2072,19 @@
         <v>46</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5307594445334815</v>
+        <v>0.5251507368944215</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01153824879420612</v>
+        <v>0.01141632036727003</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01253984260747502</v>
+        <v>0.01261942282923849</v>
       </c>
       <c r="H37" t="n">
-        <v>0.007814375205839401</v>
+        <v>0.007668814370167605</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01526212238257284</v>
+        <v>0.01516382636437246</v>
       </c>
     </row>
     <row r="38">
@@ -2171,19 +2171,19 @@
         <v>46</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4164867282452374</v>
+        <v>0.4175393598241847</v>
       </c>
       <c r="F40" t="n">
-        <v>0.009054059309679074</v>
+        <v>0.009076942604873581</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01777289056916365</v>
+        <v>0.01776164815383212</v>
       </c>
       <c r="H40" t="n">
-        <v>0.003776162301626675</v>
+        <v>0.003802384182067664</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01433195631773147</v>
+        <v>0.0143515010276795</v>
       </c>
     </row>
     <row r="41">
@@ -2204,19 +2204,19 @@
         <v>46</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2824634782292873</v>
+        <v>0.2870195542894</v>
       </c>
       <c r="F41" t="n">
-        <v>0.006140510396288854</v>
+        <v>0.006239555528030435</v>
       </c>
       <c r="G41" t="n">
-        <v>0.006729612763590792</v>
+        <v>0.00670522130254204</v>
       </c>
       <c r="H41" t="n">
-        <v>0.004142062089183879</v>
+        <v>0.004248350590752683</v>
       </c>
       <c r="I41" t="n">
-        <v>0.008138958703393829</v>
+        <v>0.008230760465308188</v>
       </c>
     </row>
     <row r="42">
@@ -2303,19 +2303,19 @@
         <v>46</v>
       </c>
       <c r="E44" t="n">
-        <v>3.985811120309127</v>
+        <v>3.963083847581854</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1245565975096602</v>
+        <v>0.1238463702369329</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1821462193517442</v>
+        <v>0.1803965351382994</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0588858824454551</v>
+        <v>0.05880648360190088</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1902273125738653</v>
+        <v>0.188886256871965</v>
       </c>
     </row>
     <row r="45">
@@ -2336,19 +2336,19 @@
         <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>7.93294682345218</v>
+        <v>6.692918204645861</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2479045882328806</v>
+        <v>0.2091536938951832</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2433258009225188</v>
+        <v>0.2002558798916727</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1601762818369389</v>
+        <v>0.1369537499430015</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3356328946288224</v>
+        <v>0.2813536378473648</v>
       </c>
     </row>
     <row r="46">
@@ -2369,19 +2369,19 @@
         <v>46</v>
       </c>
       <c r="E46" t="n">
-        <v>0.09779367918902802</v>
+        <v>0.1234347048300537</v>
       </c>
       <c r="F46" t="n">
-        <v>0.003056052474657126</v>
+        <v>0.003857334525939177</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0120406806406054</v>
+        <v>0.01566212026312117</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.007397180774450828</v>
+        <v>0.009504131043381658</v>
       </c>
     </row>
     <row r="47">
@@ -2402,19 +2402,19 @@
         <v>46</v>
       </c>
       <c r="E47" t="n">
-        <v>15.38315468130243</v>
+        <v>15.94160965159141</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4807235837907011</v>
+        <v>0.4981753016122314</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2996056386299306</v>
+        <v>0.3090089517226574</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3727042321065457</v>
+        <v>0.3867656940283394</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5887429354748565</v>
+        <v>0.6095849091961235</v>
       </c>
     </row>
     <row r="48">
@@ -2435,19 +2435,19 @@
         <v>46</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7460366744883993</v>
+        <v>0.7731283459196934</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02331364607776248</v>
+        <v>0.02416026080999042</v>
       </c>
       <c r="G48" t="n">
-        <v>0.03467917888110968</v>
+        <v>0.03501774674222304</v>
       </c>
       <c r="H48" t="n">
-        <v>0.01081046877840809</v>
+        <v>0.01153501677976342</v>
       </c>
       <c r="I48" t="n">
-        <v>0.03581682337711686</v>
+        <v>0.03678550484021742</v>
       </c>
     </row>
     <row r="49">
@@ -2468,19 +2468,19 @@
         <v>46</v>
       </c>
       <c r="E49" t="n">
-        <v>3.854257021258832</v>
+        <v>4.505825245431133</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1204455319143385</v>
+        <v>0.1408070389197229</v>
       </c>
       <c r="G49" t="n">
-        <v>0.139069653015201</v>
+        <v>0.170259809933709</v>
       </c>
       <c r="H49" t="n">
-        <v>0.07030557518208978</v>
+        <v>0.07942183144829892</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1705854886465872</v>
+        <v>0.2021922463911469</v>
       </c>
     </row>
     <row r="50">
@@ -2567,19 +2567,19 @@
         <v>46</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7267796067929644</v>
+        <v>0.6932962722522844</v>
       </c>
       <c r="F52" t="n">
-        <v>0.01579955666941227</v>
+        <v>0.01507165809244096</v>
       </c>
       <c r="G52" t="n">
-        <v>0.01707280980081607</v>
+        <v>0.01698794168639169</v>
       </c>
       <c r="H52" t="n">
-        <v>0.01072955798708678</v>
+        <v>0.01002686212913613</v>
       </c>
       <c r="I52" t="n">
-        <v>0.02086955535173775</v>
+        <v>0.0201164540557458</v>
       </c>
     </row>
     <row r="53">
@@ -2600,19 +2600,19 @@
         <v>46</v>
       </c>
       <c r="E53" t="n">
-        <v>5.875940471294936</v>
+        <v>5.873023544136841</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1277378363324986</v>
+        <v>0.12767442487254</v>
       </c>
       <c r="G53" t="n">
-        <v>0.08433902303375547</v>
+        <v>0.08471899008910609</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1026922380602493</v>
+        <v>0.1025159903130932</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1527834346047479</v>
+        <v>0.1528328594319869</v>
       </c>
     </row>
     <row r="54">
@@ -2666,19 +2666,19 @@
         <v>46</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4052426007160604</v>
+        <v>0.4037142202609881</v>
       </c>
       <c r="F55" t="n">
-        <v>0.008809621754696966</v>
+        <v>0.008776396092630175</v>
       </c>
       <c r="G55" t="n">
-        <v>0.01307424393051042</v>
+        <v>0.01330606422043588</v>
       </c>
       <c r="H55" t="n">
-        <v>0.004927050562641549</v>
+        <v>0.004824982772174649</v>
       </c>
       <c r="I55" t="n">
-        <v>0.01269219294675238</v>
+        <v>0.0127278094130857</v>
       </c>
     </row>
     <row r="56">
@@ -2699,19 +2699,19 @@
         <v>46</v>
       </c>
       <c r="E56" t="n">
-        <v>34.58336535140028</v>
+        <v>34.57404200973541</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7518122902478322</v>
+        <v>0.7516096089072917</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1579885546363571</v>
+        <v>0.1580773873764796</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7048954808196295</v>
+        <v>0.704666419411565</v>
       </c>
       <c r="I56" t="n">
-        <v>0.798729099676035</v>
+        <v>0.7985527984030183</v>
       </c>
     </row>
     <row r="57">
@@ -2732,19 +2732,19 @@
         <v>46</v>
       </c>
       <c r="E57" t="n">
-        <v>3.852255735377151</v>
+        <v>3.899507719195867</v>
       </c>
       <c r="F57" t="n">
-        <v>0.08374468989950327</v>
+        <v>0.08477190693904059</v>
       </c>
       <c r="G57" t="n">
-        <v>0.06825947627663302</v>
+        <v>0.06842986777659434</v>
       </c>
       <c r="H57" t="n">
-        <v>0.06347412759509483</v>
+        <v>0.0644507446050903</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1040152522039117</v>
+        <v>0.1050930692729909</v>
       </c>
     </row>
     <row r="58">
@@ -2831,19 +2831,19 @@
         <v>46</v>
       </c>
       <c r="E60" t="n">
-        <v>1.540040326121489</v>
+        <v>1.241495809255916</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0334791375243802</v>
+        <v>0.02698903933165036</v>
       </c>
       <c r="G60" t="n">
-        <v>0.03910884064433324</v>
+        <v>0.03698469531644999</v>
       </c>
       <c r="H60" t="n">
-        <v>0.02186524544408716</v>
+        <v>0.01600594055012183</v>
       </c>
       <c r="I60" t="n">
-        <v>0.04509302960467323</v>
+        <v>0.03797213811317888</v>
       </c>
     </row>
     <row r="61">
@@ -2864,19 +2864,19 @@
         <v>46</v>
       </c>
       <c r="E61" t="n">
-        <v>1.826264555884017</v>
+        <v>1.765045723484065</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03970140338878297</v>
+        <v>0.03837055920617533</v>
       </c>
       <c r="G61" t="n">
-        <v>0.02940813327588939</v>
+        <v>0.03011998964778197</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0309682658034697</v>
+        <v>0.02942602637253404</v>
       </c>
       <c r="I61" t="n">
-        <v>0.04843454097409625</v>
+        <v>0.04731509203981661</v>
       </c>
     </row>
     <row r="62">
@@ -2897,19 +2897,19 @@
         <v>46</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5798779361670832</v>
+        <v>0.5749247605146887</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01260604209058877</v>
+        <v>0.01249836435901497</v>
       </c>
       <c r="G62" t="n">
-        <v>0.01303647229379096</v>
+        <v>0.0129612812779134</v>
       </c>
       <c r="H62" t="n">
-        <v>0.008734687690065095</v>
+        <v>0.008649338933971584</v>
       </c>
       <c r="I62" t="n">
-        <v>0.01647739649111243</v>
+        <v>0.01634738978405836</v>
       </c>
     </row>
     <row r="63">
@@ -2930,19 +2930,19 @@
         <v>46</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9590180177447236</v>
+        <v>0.5463013159301908</v>
       </c>
       <c r="F63" t="n">
-        <v>0.02084821777705921</v>
+        <v>0.0118761155636998</v>
       </c>
       <c r="G63" t="n">
-        <v>0.05060219749165498</v>
+        <v>0.01842648371747388</v>
       </c>
       <c r="H63" t="n">
-        <v>0.005821220018717061</v>
+        <v>0.006404125349000686</v>
       </c>
       <c r="I63" t="n">
-        <v>0.03587521553540135</v>
+        <v>0.01734810577839891</v>
       </c>
     </row>
     <row r="64">
@@ -2963,19 +2963,19 @@
         <v>46</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6079598046860382</v>
+        <v>0.5986148338965237</v>
       </c>
       <c r="F64" t="n">
-        <v>0.01321651749317474</v>
+        <v>0.01301336595427225</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01043179896886345</v>
+        <v>0.009527841405022662</v>
       </c>
       <c r="H64" t="n">
-        <v>0.01011865559208954</v>
+        <v>0.01018394631377687</v>
       </c>
       <c r="I64" t="n">
-        <v>0.01631437939425994</v>
+        <v>0.01584278559476764</v>
       </c>
     </row>
     <row r="65">
@@ -2996,19 +2996,19 @@
         <v>46</v>
       </c>
       <c r="E65" t="n">
-        <v>40.31786600237992</v>
+        <v>41.10464419990189</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8764753478778244</v>
+        <v>0.8935792217369977</v>
       </c>
       <c r="G65" t="n">
-        <v>0.07620292408577729</v>
+        <v>0.063594792269593</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8538458727526594</v>
+        <v>0.8746938995919464</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8991048230029894</v>
+        <v>0.9124645438820489</v>
       </c>
     </row>
   </sheetData>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.62 [0.52, 0.72]</t>
+          <t>0.63 [0.53, 0.73]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.93 [0.90, 0.97]</t>
+          <t>0.93 [0.89, 0.97]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3169,42 +3169,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.70 [0.65, 0.75]</t>
+          <t>0.70 [0.66, 0.75]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.70 [0.65, 0.75]</t>
+          <t>0.70 [0.66, 0.75]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.70 [0.65, 0.75]</t>
+          <t>0.70 [0.66, 0.75]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.70 [0.65, 0.75]</t>
+          <t>0.70 [0.66, 0.75]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.70 [0.65, 0.75]</t>
+          <t>0.70 [0.66, 0.75]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.70 [0.65, 0.75]</t>
+          <t>0.70 [0.66, 0.75]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.70 [0.65, 0.75]</t>
+          <t>0.70 [0.66, 0.75]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.70 [0.65, 0.75]</t>
+          <t>0.70 [0.66, 0.75]</t>
         </is>
       </c>
     </row>
@@ -3231,22 +3231,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.31 [0.26, 0.36]</t>
+          <t>0.31 [0.26, 0.37]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.86 [0.82, 0.91]</t>
+          <t>0.86 [0.82, 0.90]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.65 [0.57, 0.74]</t>
+          <t>0.65 [0.56, 0.74]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.90 [0.85, 0.95]</t>
+          <t>0.91 [0.86, 0.96]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.58 [0.52, 0.63]</t>
+          <t>0.57 [0.52, 0.63]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.71 [0.58, 0.83]</t>
+          <t>0.73 [0.61, 0.84]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.97 [0.96, 0.99]</t>
+          <t>0.96 [0.93, 0.98]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3587,19 +3587,19 @@
         <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05800883215332904</v>
+        <v>0.05906815418722734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003053096429122581</v>
+        <v>0.003108850220380386</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009180714226198402</v>
+        <v>0.009363984211029318</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007478059043031524</v>
+        <v>0.007622146139427428</v>
       </c>
     </row>
     <row r="5">
@@ -3620,19 +3620,19 @@
         <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6882022388879362</v>
+        <v>0.6869364161031261</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03622117046778611</v>
+        <v>0.03615454821595401</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04075542494289004</v>
+        <v>0.04068347668557545</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01657768443359146</v>
+        <v>0.0165457401317433</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05586465650198076</v>
+        <v>0.05576335630016471</v>
       </c>
     </row>
     <row r="6">
@@ -3686,19 +3686,19 @@
         <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>1.295872278232148</v>
+        <v>1.290928775407289</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06820380411748148</v>
+        <v>0.06794361975827838</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1178195284737383</v>
+        <v>0.1169975007588211</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01141660915208998</v>
+        <v>0.01155262946895939</v>
       </c>
       <c r="I7" t="n">
-        <v>0.124990999082873</v>
+        <v>0.1243346100475974</v>
       </c>
     </row>
     <row r="8">
@@ -3719,19 +3719,19 @@
         <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3698501241667016</v>
+        <v>0.3709094462005999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01946579600877377</v>
+        <v>0.01952154980003157</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04847236485507495</v>
+        <v>0.04849349326154734</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0428287280211208</v>
+        <v>0.0428946653783222</v>
       </c>
     </row>
     <row r="9">
@@ -3752,19 +3752,19 @@
         <v>31</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1022693216115456</v>
+        <v>0.1063600031534179</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005382595874291875</v>
+        <v>0.005597894902811468</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006762339629952767</v>
+        <v>0.007077219589779377</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002123252504284098</v>
+        <v>0.002186784250240224</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008641939244299651</v>
+        <v>0.009009005555382713</v>
       </c>
     </row>
     <row r="10">
@@ -4115,19 +4115,19 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>19.41652497158246</v>
+        <v>19.13229230228862</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9708262485791229</v>
+        <v>0.9566146151144311</v>
       </c>
       <c r="G20" t="n">
-        <v>0.03329226488113525</v>
+        <v>0.05201130687153104</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9552449889924036</v>
+        <v>0.9322725742018273</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9864075081658422</v>
+        <v>0.980956656027035</v>
       </c>
     </row>
     <row r="21">
@@ -4148,19 +4148,19 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2012776002688419</v>
+        <v>0.2460264363384327</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0100638800134421</v>
+        <v>0.01230132181692164</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01920938351073076</v>
+        <v>0.02612117144033974</v>
       </c>
       <c r="H21" t="n">
-        <v>0.001073611791974851</v>
+        <v>7.623727027807753e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01905414823490934</v>
+        <v>0.0245264063635652</v>
       </c>
     </row>
     <row r="22">
@@ -4280,19 +4280,19 @@
         <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3423268504116201</v>
+        <v>0.5818106836358669</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01711634252058101</v>
+        <v>0.02909053418179334</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02175982983579709</v>
+        <v>0.03359494375672264</v>
       </c>
       <c r="H25" t="n">
-        <v>0.006932428676181976</v>
+        <v>0.01336761652078021</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02730025636498004</v>
+        <v>0.04481345184280647</v>
       </c>
     </row>
     <row r="26">
@@ -4379,19 +4379,19 @@
         <v>31</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1375495121828079</v>
+        <v>0.1703071982356228</v>
       </c>
       <c r="F28" t="n">
-        <v>0.004437081038155093</v>
+        <v>0.005493780588245898</v>
       </c>
       <c r="G28" t="n">
-        <v>0.008176751298000664</v>
+        <v>0.0114564789264819</v>
       </c>
       <c r="H28" t="n">
-        <v>0.001437824447949075</v>
+        <v>0.001291510191540921</v>
       </c>
       <c r="I28" t="n">
-        <v>0.00743633762836111</v>
+        <v>0.009696050984950876</v>
       </c>
     </row>
     <row r="29">
@@ -4412,19 +4412,19 @@
         <v>31</v>
       </c>
       <c r="E29" t="n">
-        <v>17.85185380833014</v>
+        <v>17.81143749432163</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5758662518816173</v>
+        <v>0.5745624998168268</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1398708840799325</v>
+        <v>0.1387478356855976</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5245611973965609</v>
+        <v>0.5236693828085349</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6271713063666737</v>
+        <v>0.6254556168251187</v>
       </c>
     </row>
     <row r="30">
@@ -4478,19 +4478,19 @@
         <v>31</v>
       </c>
       <c r="E31" t="n">
-        <v>1.515819825255375</v>
+        <v>1.47633980546478</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0488974137179153</v>
+        <v>0.04762386469241227</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06878290293429819</v>
+        <v>0.06855929231217835</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02366764123240049</v>
+        <v>0.02247611324527697</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07412718620343012</v>
+        <v>0.07277161613954757</v>
       </c>
     </row>
     <row r="32">
@@ -4511,19 +4511,19 @@
         <v>31</v>
       </c>
       <c r="E32" t="n">
-        <v>4.897283478754927</v>
+        <v>4.891363739331405</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1579768864114493</v>
+        <v>0.1577859270752066</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1122724292163547</v>
+        <v>0.1122954637305723</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1167950268986221</v>
+        <v>0.1165956184343515</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1991587459242765</v>
+        <v>0.1989762357160617</v>
       </c>
     </row>
     <row r="33">
@@ -4544,19 +4544,19 @@
         <v>31</v>
       </c>
       <c r="E33" t="n">
-        <v>6.149519539718669</v>
+        <v>6.202577926888475</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1983715980554409</v>
+        <v>0.2000831589318863</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1327780119875602</v>
+        <v>0.1333668607660262</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1496682300582367</v>
+        <v>0.1511637994589623</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2470749660526451</v>
+        <v>0.2490025184048103</v>
       </c>
     </row>
     <row r="34">
@@ -4676,19 +4676,19 @@
         <v>31</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6014461866513275</v>
+        <v>0.5991357718726141</v>
       </c>
       <c r="F37" t="n">
-        <v>0.02004820622171092</v>
+        <v>0.0199711923957538</v>
       </c>
       <c r="G37" t="n">
-        <v>0.05574497076908215</v>
+        <v>0.0556181089471215</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.04086372040028709</v>
+        <v>0.04073933559148955</v>
       </c>
     </row>
     <row r="38">
@@ -4709,19 +4709,19 @@
         <v>31</v>
       </c>
       <c r="E38" t="n">
-        <v>28.51377329282768</v>
+        <v>28.51361311342675</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9504591097609226</v>
+        <v>0.9504537704475583</v>
       </c>
       <c r="G38" t="n">
-        <v>0.120634351694573</v>
+        <v>0.1206321529206997</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9054135025343342</v>
+        <v>0.9054089842566275</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9955047169875111</v>
+        <v>0.9954985566384891</v>
       </c>
     </row>
     <row r="39">
@@ -4808,19 +4808,19 @@
         <v>31</v>
       </c>
       <c r="E41" t="n">
-        <v>0.02155690281545929</v>
+        <v>0.02402749699510181</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0007185634271819764</v>
+        <v>0.0008009165665033936</v>
       </c>
       <c r="G41" t="n">
-        <v>0.001231027921418992</v>
+        <v>0.00124947122158385</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0002588900468035567</v>
+        <v>0.0003343563446613442</v>
       </c>
       <c r="I41" t="n">
-        <v>0.001178236807560396</v>
+        <v>0.001267476788345443</v>
       </c>
     </row>
     <row r="42">
@@ -4907,19 +4907,19 @@
         <v>31</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6737486626012527</v>
+        <v>0.6832522517226762</v>
       </c>
       <c r="F44" t="n">
-        <v>0.02323271250349147</v>
+        <v>0.02356042247319573</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06653609616590385</v>
+        <v>0.06833895402398364</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0485416899358712</v>
+        <v>0.0495551703591073</v>
       </c>
     </row>
     <row r="45">
@@ -4940,19 +4940,19 @@
         <v>31</v>
       </c>
       <c r="E45" t="n">
-        <v>1.931351307662053</v>
+        <v>1.556102019247919</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06659832095386391</v>
+        <v>0.05365869031889376</v>
       </c>
       <c r="G45" t="n">
-        <v>0.09843972026326031</v>
+        <v>0.07851001969182689</v>
       </c>
       <c r="H45" t="n">
-        <v>0.02915385393282847</v>
+        <v>0.02379507596373763</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1040427879748993</v>
+        <v>0.08352230467404989</v>
       </c>
     </row>
     <row r="46">
@@ -5006,19 +5006,19 @@
         <v>31</v>
       </c>
       <c r="E47" t="n">
-        <v>20.47400287019498</v>
+        <v>21.04524653841536</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7060000989722408</v>
+        <v>0.7256981564970812</v>
       </c>
       <c r="G47" t="n">
-        <v>0.321427146866539</v>
+        <v>0.3070577948459663</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5837357511223863</v>
+        <v>0.6088996178389743</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8282644468220953</v>
+        <v>0.8424966951551882</v>
       </c>
     </row>
     <row r="48">
@@ -5072,19 +5072,19 @@
         <v>31</v>
       </c>
       <c r="E49" t="n">
-        <v>4.451922718465823</v>
+        <v>4.246424749538159</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1535145764988215</v>
+        <v>0.1464284396392468</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2536549882210088</v>
+        <v>0.2498081525633519</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05702937910327856</v>
+        <v>0.05140650027139095</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2499997738943644</v>
+        <v>0.2414503790071028</v>
       </c>
     </row>
     <row r="50">
@@ -5171,19 +5171,19 @@
         <v>31</v>
       </c>
       <c r="E52" t="n">
-        <v>0.03529845586171755</v>
+        <v>0.03263888139363245</v>
       </c>
       <c r="F52" t="n">
-        <v>0.001138659866507018</v>
+        <v>0.001052867141730079</v>
       </c>
       <c r="G52" t="n">
-        <v>0.004421229351924983</v>
+        <v>0.004416534321522651</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0.002760379885534091</v>
+        <v>0.00267286500970202</v>
       </c>
     </row>
     <row r="53">
@@ -5204,19 +5204,19 @@
         <v>31</v>
       </c>
       <c r="E53" t="n">
-        <v>5.244868196145869</v>
+        <v>5.235266516899406</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1691892966498667</v>
+        <v>0.1688795650612712</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1105063637006991</v>
+        <v>0.1104119271788722</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1286552351980936</v>
+        <v>0.1283801432053623</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2097233581016399</v>
+        <v>0.20937898691718</v>
       </c>
     </row>
     <row r="54">
@@ -5270,19 +5270,19 @@
         <v>31</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1448013682977464</v>
+        <v>0.1472961417193253</v>
       </c>
       <c r="F55" t="n">
-        <v>0.004671011880572466</v>
+        <v>0.00475148844255888</v>
       </c>
       <c r="G55" t="n">
-        <v>0.009266741829836564</v>
+        <v>0.009233125244555536</v>
       </c>
       <c r="H55" t="n">
-        <v>0.001271943535461986</v>
+        <v>0.00136475076047945</v>
       </c>
       <c r="I55" t="n">
-        <v>0.008070080225682945</v>
+        <v>0.00813822612463831</v>
       </c>
     </row>
     <row r="56">
@@ -5303,19 +5303,19 @@
         <v>31</v>
       </c>
       <c r="E56" t="n">
-        <v>23.03742498350323</v>
+        <v>23.0444610718924</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7431427414033298</v>
+        <v>0.7433697119965291</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1432864540681305</v>
+        <v>0.1433223872819523</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6905848457319557</v>
+        <v>0.6907986359159148</v>
       </c>
       <c r="I56" t="n">
-        <v>0.795700637074704</v>
+        <v>0.7959407880771434</v>
       </c>
     </row>
     <row r="57">
@@ -5336,19 +5336,19 @@
         <v>31</v>
       </c>
       <c r="E57" t="n">
-        <v>1.879175100628323</v>
+        <v>1.881905492532117</v>
       </c>
       <c r="F57" t="n">
-        <v>0.06061855163317171</v>
+        <v>0.06070662879135863</v>
       </c>
       <c r="G57" t="n">
-        <v>0.06158267477633991</v>
+        <v>0.06152061358280512</v>
       </c>
       <c r="H57" t="n">
-        <v>0.03802984415828327</v>
+        <v>0.03814068554604273</v>
       </c>
       <c r="I57" t="n">
-        <v>0.08320725910806015</v>
+        <v>0.08327257203667453</v>
       </c>
     </row>
     <row r="58">
@@ -5402,19 +5402,19 @@
         <v>31</v>
       </c>
       <c r="E59" t="n">
-        <v>0.004008016032064128</v>
+        <v>0.008016032064128256</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0001292908397440041</v>
+        <v>0.0002585816794880083</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0007198609299670337</v>
+        <v>0.001439721859934067</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0003933379606052412</v>
+        <v>0.0007866759212104824</v>
       </c>
     </row>
     <row r="60">
@@ -5435,19 +5435,19 @@
         <v>31</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2398560073134023</v>
+        <v>0.2214631462810678</v>
       </c>
       <c r="F60" t="n">
-        <v>0.007737290558496848</v>
+        <v>0.007143972460679607</v>
       </c>
       <c r="G60" t="n">
-        <v>0.01532295239320369</v>
+        <v>0.01534428140810426</v>
       </c>
       <c r="H60" t="n">
-        <v>0.002116786244275318</v>
+        <v>0.001515644600630189</v>
       </c>
       <c r="I60" t="n">
-        <v>0.01335779487271838</v>
+        <v>0.01277230032072903</v>
       </c>
     </row>
     <row r="61">
@@ -5468,19 +5468,19 @@
         <v>31</v>
       </c>
       <c r="E61" t="n">
-        <v>3.283726509254223</v>
+        <v>3.187051736060256</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1059266615888459</v>
+        <v>0.1028081205180728</v>
       </c>
       <c r="G61" t="n">
-        <v>0.08370481213813216</v>
+        <v>0.08127352862694047</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0752234886185936</v>
+        <v>0.07299674953957039</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1366298345590982</v>
+        <v>0.1326194914965751</v>
       </c>
     </row>
     <row r="62">
@@ -5501,19 +5501,19 @@
         <v>31</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1126680075516603</v>
+        <v>0.1145129540095993</v>
       </c>
       <c r="F62" t="n">
-        <v>0.003634451856505171</v>
+        <v>0.003693966258374173</v>
       </c>
       <c r="G62" t="n">
-        <v>0.004478237840531332</v>
+        <v>0.004446985600544132</v>
       </c>
       <c r="H62" t="n">
-        <v>0.001991820955036058</v>
+        <v>0.002062798771080716</v>
       </c>
       <c r="I62" t="n">
-        <v>0.005277082757974283</v>
+        <v>0.005325133745667629</v>
       </c>
     </row>
     <row r="63">
@@ -5534,19 +5534,19 @@
         <v>31</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7870045245643215</v>
+        <v>0.8510817874000766</v>
       </c>
       <c r="F63" t="n">
-        <v>0.02538724272788134</v>
+        <v>0.02745425120645408</v>
       </c>
       <c r="G63" t="n">
-        <v>0.02467041407200153</v>
+        <v>0.02465359934200199</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01633806178891182</v>
+        <v>0.01841123796024245</v>
       </c>
       <c r="I63" t="n">
-        <v>0.03443642366685085</v>
+        <v>0.03649726445266572</v>
       </c>
     </row>
     <row r="64">
@@ -5567,19 +5567,19 @@
         <v>31</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6398074359218365</v>
+        <v>0.6322853458267436</v>
       </c>
       <c r="F64" t="n">
-        <v>0.02063894954586569</v>
+        <v>0.02039630147828205</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01916779383403519</v>
+        <v>0.01895500647757809</v>
       </c>
       <c r="H64" t="n">
-        <v>0.01360814600528384</v>
+        <v>0.0134435489701833</v>
       </c>
       <c r="I64" t="n">
-        <v>0.02766975308644754</v>
+        <v>0.02734905398638081</v>
       </c>
     </row>
     <row r="65">
@@ -5600,19 +5600,19 @@
         <v>31</v>
       </c>
       <c r="E65" t="n">
-        <v>25.88679651334709</v>
+        <v>25.93945601234272</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8350579520434545</v>
+        <v>0.8367566455594427</v>
       </c>
       <c r="G65" t="n">
-        <v>0.09805822056876318</v>
+        <v>0.1010150529109589</v>
       </c>
       <c r="H65" t="n">
-        <v>0.7990899063555967</v>
+        <v>0.7997040250122966</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8710259977313122</v>
+        <v>0.8738092661065888</v>
       </c>
     </row>
   </sheetData>
@@ -5679,42 +5679,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.80 [0.77, 0.82]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.80 [0.77, 0.82]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.80 [0.77, 0.82]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.80 [0.77, 0.82]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.80 [0.77, 0.82]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.80 [0.77, 0.82]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.80 [0.77, 0.82]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.78 [0.74, 0.82]</t>
+          <t>0.80 [0.77, 0.82]</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.86 [0.76, 0.97]</t>
+          <t>0.91 [0.89, 0.93]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.18 [0.02, 0.34]</t>
+          <t>0.16 [0.00, 0.33]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -5765,42 +5765,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.69 [0.64, 0.74]</t>
+          <t>0.71 [0.68, 0.74]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.69 [0.64, 0.74]</t>
+          <t>0.71 [0.68, 0.74]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.69 [0.64, 0.74]</t>
+          <t>0.71 [0.68, 0.74]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.69 [0.64, 0.74]</t>
+          <t>0.71 [0.68, 0.74]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.69 [0.64, 0.74]</t>
+          <t>0.71 [0.68, 0.74]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.69 [0.64, 0.74]</t>
+          <t>0.71 [0.68, 0.74]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.69 [0.64, 0.74]</t>
+          <t>0.71 [0.68, 0.74]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.69 [0.64, 0.74]</t>
+          <t>0.71 [0.68, 0.74]</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.90 [0.89, 0.92]</t>
+          <t>0.90 [0.88, 0.92]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.96 [0.96, 0.97]</t>
+          <t>0.96 [0.95, 0.97]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.23 [0.01, 0.44]</t>
+          <t>0.27 [0.00, 0.57]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -5866,17 +5866,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.67 [0.60, 0.74]</t>
+          <t>0.66 [0.59, 0.73]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.82 [0.72, 0.93]</t>
+          <t>0.87 [0.84, 0.91]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.26 [0.07, 0.44]</t>
+          <t>0.20 [0.03, 0.38]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -6456,19 +6456,19 @@
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>12.06543987482939</v>
+        <v>11.93246263897544</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6703022152682993</v>
+        <v>0.6629145910541911</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1405781904514687</v>
+        <v>0.1444214244031252</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6003943258213822</v>
+        <v>0.5910955063262123</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7402101047152163</v>
+        <v>0.73473367578217</v>
       </c>
     </row>
     <row r="14">
@@ -6522,19 +6522,19 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3063306832056832</v>
+        <v>0.1863306832056832</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01701837128920462</v>
+        <v>0.01035170462253795</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03752584802705606</v>
+        <v>0.02746508660951009</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03567953648739301</v>
+        <v>0.02400977087151616</v>
       </c>
     </row>
     <row r="16">
@@ -6555,19 +6555,19 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>4.056629531970461</v>
+        <v>4.039558931338216</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2253683073316922</v>
+        <v>0.2244199406299009</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1042199798015807</v>
+        <v>0.1064049045544394</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1735409306758227</v>
+        <v>0.1715060264564965</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2771956839875618</v>
+        <v>0.2773338548033053</v>
       </c>
     </row>
     <row r="17">
@@ -6588,19 +6588,19 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>1.562750352472345</v>
+        <v>1.832798188958537</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08681946402624137</v>
+        <v>0.1018221216088076</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1017874907343491</v>
+        <v>0.1037502925510623</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03620173572511832</v>
+        <v>0.0502283149276149</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1374371923273644</v>
+        <v>0.1534159282900003</v>
       </c>
     </row>
     <row r="18">
@@ -6984,19 +6984,19 @@
         <v>18</v>
       </c>
       <c r="E29" t="n">
-        <v>4.383459595959596</v>
+        <v>4.915205627705628</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3371891996891997</v>
+        <v>0.3780927405927406</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2174732764476325</v>
+        <v>0.2963268565593948</v>
       </c>
       <c r="H29" t="n">
-        <v>0.205771413993476</v>
+        <v>0.1990242133358417</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4686069853849233</v>
+        <v>0.5571612678496396</v>
       </c>
     </row>
     <row r="30">
@@ -7050,19 +7050,19 @@
         <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>3.315079365079365</v>
+        <v>2.616666666666667</v>
       </c>
       <c r="F31" t="n">
-        <v>0.255006105006105</v>
+        <v>0.2012820512820513</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3120342139873191</v>
+        <v>0.2879158161359522</v>
       </c>
       <c r="H31" t="n">
-        <v>0.06644571665239618</v>
+        <v>0.02729626488371584</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4435664933598139</v>
+        <v>0.3752678376803867</v>
       </c>
     </row>
     <row r="32">
@@ -7116,19 +7116,19 @@
         <v>18</v>
       </c>
       <c r="E33" t="n">
-        <v>3.73538961038961</v>
+        <v>3.902056277056277</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2873376623376623</v>
+        <v>0.3001581751581751</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3660621297328293</v>
+        <v>0.3859921845880024</v>
       </c>
       <c r="H33" t="n">
-        <v>0.06612853125560353</v>
+        <v>0.0669054324625678</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5085467934197212</v>
+        <v>0.5334109178537825</v>
       </c>
     </row>
     <row r="34">
@@ -7248,19 +7248,19 @@
         <v>18</v>
       </c>
       <c r="E37" t="n">
-        <v>2.914091351916052</v>
+        <v>2.885839256080796</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1618939639953362</v>
+        <v>0.1603244031155998</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0724134238601382</v>
+        <v>0.07341422249556045</v>
       </c>
       <c r="H37" t="n">
-        <v>0.125883615495119</v>
+        <v>0.1238163691626176</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1979043124955534</v>
+        <v>0.196832437068582</v>
       </c>
     </row>
     <row r="38">
@@ -7314,19 +7314,19 @@
         <v>18</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1196632869987004</v>
+        <v>0.02365814907929826</v>
       </c>
       <c r="F39" t="n">
-        <v>0.006647960388816689</v>
+        <v>0.00131434161551657</v>
       </c>
       <c r="G39" t="n">
-        <v>0.02308004010729743</v>
+        <v>0.00353994337777871</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.01812539431416215</v>
+        <v>0.003074714042472325</v>
       </c>
     </row>
     <row r="40">
@@ -7347,19 +7347,19 @@
         <v>18</v>
       </c>
       <c r="E40" t="n">
-        <v>13.87501467578211</v>
+        <v>13.89496938356018</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7708341486545618</v>
+        <v>0.771942743531121</v>
       </c>
       <c r="G40" t="n">
-        <v>0.08149211291501537</v>
+        <v>0.08157728523161939</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7303090743015432</v>
+        <v>0.7313753139815106</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8113592230075803</v>
+        <v>0.8125101730807315</v>
       </c>
     </row>
     <row r="41">
@@ -7380,19 +7380,19 @@
         <v>18</v>
       </c>
       <c r="E41" t="n">
-        <v>1.07236163768409</v>
+        <v>1.17666416366068</v>
       </c>
       <c r="F41" t="n">
-        <v>0.05957564653800498</v>
+        <v>0.06537023131448222</v>
       </c>
       <c r="G41" t="n">
-        <v>0.03205784357997013</v>
+        <v>0.02994824146338071</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04363365597959899</v>
+        <v>0.0504773212078155</v>
       </c>
       <c r="I41" t="n">
-        <v>0.07551763709641097</v>
+        <v>0.08026314142114893</v>
       </c>
     </row>
     <row r="42">
@@ -7512,19 +7512,19 @@
         <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>1.719518523357016</v>
+        <v>1.644091041967675</v>
       </c>
       <c r="F45" t="n">
-        <v>0.09552880685316756</v>
+        <v>0.09133839122042636</v>
       </c>
       <c r="G45" t="n">
-        <v>0.05992118771571776</v>
+        <v>0.0588953569064011</v>
       </c>
       <c r="H45" t="n">
-        <v>0.06573070123731455</v>
+        <v>0.06205041926455745</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1253269124690206</v>
+        <v>0.1206263631762953</v>
       </c>
     </row>
     <row r="46">
@@ -7578,19 +7578,19 @@
         <v>18</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9570043253098853</v>
+        <v>0.1446124469387051</v>
       </c>
       <c r="F47" t="n">
-        <v>0.05316690696166029</v>
+        <v>0.008034024829928063</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1816465806156674</v>
+        <v>0.01683437949664067</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1434976263663496</v>
+        <v>0.01640556480337</v>
       </c>
     </row>
     <row r="48">
@@ -7611,19 +7611,19 @@
         <v>18</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3554925037092719</v>
+        <v>0.3891953490630654</v>
       </c>
       <c r="F48" t="n">
-        <v>0.01974958353940399</v>
+        <v>0.02162196383683697</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01343656374934449</v>
+        <v>0.01913933121557701</v>
       </c>
       <c r="H48" t="n">
-        <v>0.01306773758507079</v>
+        <v>0.01210419833985971</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0264314294937372</v>
+        <v>0.03113972933381423</v>
       </c>
     </row>
     <row r="49">
@@ -7644,19 +7644,19 @@
         <v>18</v>
       </c>
       <c r="E49" t="n">
-        <v>14.83851314152945</v>
+        <v>15.69262965593618</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8243618411960807</v>
+        <v>0.8718127586631211</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2159421929266566</v>
+        <v>0.06894086614378828</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7169763150233484</v>
+        <v>0.8375292724887954</v>
       </c>
       <c r="I49" t="n">
-        <v>0.931747367368813</v>
+        <v>0.9060962448374469</v>
       </c>
     </row>
   </sheetData>
